--- a/figures_updated/Fig6_stats.xlsx
+++ b/figures_updated/Fig6_stats.xlsx
@@ -458,13 +458,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00343206230906231</v>
+        <v>0.0138931406884598</v>
       </c>
       <c r="E2" t="n">
-        <v>0.182423563713841</v>
+        <v>0.127128329815822</v>
       </c>
     </row>
     <row r="3">
@@ -478,10 +478,10 @@
         <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0124054746999947</v>
+        <v>0.008595566090867</v>
       </c>
       <c r="E3" t="n">
-        <v>0.108366673944132</v>
+        <v>0.118983929111286</v>
       </c>
     </row>
   </sheetData>
@@ -523,16 +523,16 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>2.5477507984191</v>
+        <v>3.30023245073812</v>
       </c>
       <c r="D2" t="n">
-        <v>1.59802245017538</v>
+        <v>1.60066481928194</v>
       </c>
       <c r="E2" t="n">
-        <v>1.59431477207312</v>
+        <v>2.06178858370774</v>
       </c>
       <c r="F2" t="n">
-        <v>0.118364213663889</v>
+        <v>0.0451650702626159</v>
       </c>
     </row>
     <row r="3">
@@ -543,16 +543,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.332759629512227</v>
+        <v>0.289079176767594</v>
       </c>
       <c r="D3" t="n">
-        <v>0.108700039548144</v>
+        <v>0.114194319150924</v>
       </c>
       <c r="E3" t="n">
-        <v>3.06126502709177</v>
+        <v>2.53146722986749</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00383391865185939</v>
+        <v>0.0150064258397599</v>
       </c>
     </row>
     <row r="4">
@@ -563,16 +563,16 @@
         <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>30.0517734718559</v>
+        <v>30.3031008275229</v>
       </c>
       <c r="D4" t="n">
-        <v>3.95961914031948</v>
+        <v>4.13971367494397</v>
       </c>
       <c r="E4" t="n">
-        <v>7.58956162370485</v>
+        <v>7.32009583438958</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00000000211042508330004</v>
+        <v>0.00000000389152114238421</v>
       </c>
     </row>
     <row r="5">
@@ -583,16 +583,16 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>14.9774520897457</v>
+        <v>16.0464745945745</v>
       </c>
       <c r="D5" t="n">
-        <v>3.54307250123772</v>
+        <v>3.57869137880166</v>
       </c>
       <c r="E5" t="n">
-        <v>4.22724967793166</v>
+        <v>4.48389450110886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0000918084576935355</v>
+        <v>0.0000386242193299267</v>
       </c>
     </row>
     <row r="6">
@@ -603,16 +603,16 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.254668487901804</v>
+        <v>-0.276815182020781</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0994085190830165</v>
+        <v>0.102503994008108</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.56183765990045</v>
+        <v>-2.70053069345655</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0132360614364315</v>
+        <v>0.00922720689303919</v>
       </c>
     </row>
     <row r="7">
@@ -623,16 +623,16 @@
         <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>27.7620196595736</v>
+        <v>27.8107393755146</v>
       </c>
       <c r="D7" t="n">
-        <v>3.62047796785087</v>
+        <v>3.58722263821912</v>
       </c>
       <c r="E7" t="n">
-        <v>7.66805375038735</v>
+        <v>7.75272186320759</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000000000339409198107824</v>
+        <v>0.000000000247542171574673</v>
       </c>
     </row>
   </sheetData>
@@ -692,40 +692,40 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>0.594193798332085</v>
+        <v>0.565912417940592</v>
       </c>
       <c r="C2" t="n">
-        <v>0.574869693490756</v>
+        <v>0.546181164210619</v>
       </c>
       <c r="D2" t="n">
-        <v>2.07938539058593</v>
+        <v>2.21166570480553</v>
       </c>
       <c r="E2" t="n">
-        <v>30.7488395043923</v>
+        <v>28.6810167101006</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00000000595240229491053</v>
+        <v>0.0000000106341300559599</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>-95.2431507996667</v>
+        <v>-102.446158195508</v>
       </c>
       <c r="I2" t="n">
-        <v>198.486301599333</v>
+        <v>212.892316391015</v>
       </c>
       <c r="J2" t="n">
-        <v>205.712951558415</v>
+        <v>220.292906797856</v>
       </c>
       <c r="K2" t="n">
-        <v>181.601431308452</v>
+        <v>215.22446835177</v>
       </c>
       <c r="L2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -733,34 +733,34 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>0.597091766036525</v>
+        <v>0.588425021506095</v>
       </c>
       <c r="C3" t="n">
-        <v>0.582169238852692</v>
+        <v>0.573181503784098</v>
       </c>
       <c r="D3" t="n">
-        <v>2.03877367798259</v>
+        <v>2.06689566504368</v>
       </c>
       <c r="E3" t="n">
-        <v>40.012777908251</v>
+        <v>38.6016556176527</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0000000000219061399193343</v>
+        <v>0.0000000000389154478202252</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>-119.94244445127</v>
+        <v>-120.723305352376</v>
       </c>
       <c r="I3" t="n">
-        <v>247.88488890254</v>
+        <v>249.446610704751</v>
       </c>
       <c r="J3" t="n">
-        <v>256.057093973879</v>
+        <v>257.618815776089</v>
       </c>
       <c r="K3" t="n">
-        <v>224.456297941871</v>
+        <v>230.691115269523</v>
       </c>
       <c r="L3" t="n">
         <v>54</v>
@@ -799,7 +799,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>1.022</v>
+        <v>1.007</v>
       </c>
     </row>
     <row r="3">
@@ -810,7 +810,7 @@
         <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>1.022</v>
+        <v>1.007</v>
       </c>
     </row>
     <row r="4">
@@ -821,7 +821,7 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>1.066</v>
+        <v>1.032</v>
       </c>
     </row>
     <row r="5">
@@ -832,7 +832,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>1.066</v>
+        <v>1.032</v>
       </c>
     </row>
   </sheetData>
